--- a/19 GENSETS VEHICLE CONFIGURATION.xlsx
+++ b/19 GENSETS VEHICLE CONFIGURATION.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fmlfreightsolutionscom-my.sharepoint.com/personal/jason_fml-freight-solutions_com/Documents/FML-PROJECTS/LOAD-CONFIGURATOR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fmlfreightsolutionscom-my.sharepoint.com/personal/jason_fml-freight-solutions_com/Documents/FML-PROJECTS/load_configurator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45A8E224-4106-46C1-9904-56C64D7D4B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{45A8E224-4106-46C1-9904-56C64D7D4B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{419C1DAE-A148-4787-AFA8-BE4F07F2E6CA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4AA14378-C8A1-48FF-9219-D2086BF6200A}"/>
   </bookViews>
@@ -527,423 +527,423 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B027133C-7991-4109-A9C5-B10D1243D581}">
-  <dimension ref="D6:K25"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="4:10" x14ac:dyDescent="0.3">
-      <c r="D6" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>38</v>
       </c>
-      <c r="E6" t="s">
+      <c r="B1" t="s">
         <v>39</v>
       </c>
-      <c r="G6" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="H6" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="I6" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="J6" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="4:10" x14ac:dyDescent="0.3">
-      <c r="D7" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="E7" t="s">
+      <c r="B2" t="s">
         <v>0</v>
       </c>
+      <c r="D2">
+        <v>1.51</v>
+      </c>
+      <c r="E2">
+        <v>2.77</v>
+      </c>
+      <c r="F2">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="G2">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>1.881</v>
+      </c>
+      <c r="E3">
+        <v>3.38</v>
+      </c>
+      <c r="F3">
+        <v>1.17</v>
+      </c>
+      <c r="G3">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>1.3580000000000001</v>
+      </c>
+      <c r="E4">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F4">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="G4">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>3.7879999999999998</v>
+      </c>
+      <c r="E5">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="F5">
+        <v>1.63</v>
+      </c>
+      <c r="G5">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>3.7879999999999998</v>
+      </c>
+      <c r="E6">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="F6">
+        <v>1.63</v>
+      </c>
+      <c r="G6">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7">
+        <v>0.877</v>
+      </c>
+      <c r="E7">
+        <v>2.33</v>
+      </c>
+      <c r="F7">
+        <v>0.96</v>
+      </c>
       <c r="G7">
-        <v>1.51</v>
-      </c>
-      <c r="H7">
-        <v>2.77</v>
-      </c>
-      <c r="I7">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="J7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8">
+        <v>0.877</v>
+      </c>
+      <c r="E8">
+        <v>2.33</v>
+      </c>
+      <c r="F8">
+        <v>0.96</v>
+      </c>
+      <c r="G8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9">
+        <v>0.877</v>
+      </c>
+      <c r="E9">
+        <v>2.33</v>
+      </c>
+      <c r="F9">
+        <v>0.96</v>
+      </c>
+      <c r="G9">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10">
+        <v>0.83799999999999997</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>0.92</v>
+      </c>
+      <c r="G10">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11">
+        <v>0.83799999999999997</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>0.92</v>
+      </c>
+      <c r="G11">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12">
+        <v>0.83799999999999997</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>0.92</v>
+      </c>
+      <c r="G12">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13">
+        <v>5.1109999999999998</v>
+      </c>
+      <c r="E13">
+        <v>4.93</v>
+      </c>
+      <c r="F13">
+        <v>1.66</v>
+      </c>
+      <c r="G13">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="H13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14">
+        <v>4.7069999999999999</v>
+      </c>
+      <c r="E14">
+        <v>4.93</v>
+      </c>
+      <c r="F14">
+        <v>1.66</v>
+      </c>
+      <c r="G14">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="H14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15">
+        <v>5.1109999999999998</v>
+      </c>
+      <c r="E15">
+        <v>4.93</v>
+      </c>
+      <c r="F15">
+        <v>1.66</v>
+      </c>
+      <c r="G15">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="H15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16">
+        <v>3.8079999999999998</v>
+      </c>
+      <c r="E16">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="F16">
         <v>1.63</v>
       </c>
-    </row>
-    <row r="8" spans="4:10" x14ac:dyDescent="0.3">
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8">
-        <v>1.881</v>
-      </c>
-      <c r="H8">
+      <c r="G16">
+        <v>2.36</v>
+      </c>
+      <c r="H16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17">
+        <v>1.196</v>
+      </c>
+      <c r="E17">
+        <v>2.8</v>
+      </c>
+      <c r="F17">
+        <v>1.05</v>
+      </c>
+      <c r="G17">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18">
+        <v>1.88</v>
+      </c>
+      <c r="E18">
         <v>3.38</v>
       </c>
-      <c r="I8">
+      <c r="F18">
         <v>1.17</v>
       </c>
-      <c r="J8">
+      <c r="G18">
         <v>1.85</v>
       </c>
     </row>
-    <row r="9" spans="4:10" x14ac:dyDescent="0.3">
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9">
-        <v>1.3580000000000001</v>
-      </c>
-      <c r="H9">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="I9">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="J9">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="10" spans="4:10" x14ac:dyDescent="0.3">
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10">
-        <v>3.7879999999999998</v>
-      </c>
-      <c r="H10">
-        <v>4.7699999999999996</v>
-      </c>
-      <c r="I10">
-        <v>1.63</v>
-      </c>
-      <c r="J10">
-        <v>2.36</v>
-      </c>
-    </row>
-    <row r="11" spans="4:10" x14ac:dyDescent="0.3">
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="G11">
-        <v>3.7879999999999998</v>
-      </c>
-      <c r="H11">
-        <v>4.7699999999999996</v>
-      </c>
-      <c r="I11">
-        <v>1.63</v>
-      </c>
-      <c r="J11">
-        <v>2.36</v>
-      </c>
-    </row>
-    <row r="12" spans="4:10" x14ac:dyDescent="0.3">
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12">
-        <v>0.877</v>
-      </c>
-      <c r="H12">
-        <v>2.33</v>
-      </c>
-      <c r="I12">
-        <v>0.96</v>
-      </c>
-      <c r="J12">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="13" spans="4:10" x14ac:dyDescent="0.3">
-      <c r="D13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13">
-        <v>0.877</v>
-      </c>
-      <c r="H13">
-        <v>2.33</v>
-      </c>
-      <c r="I13">
-        <v>0.96</v>
-      </c>
-      <c r="J13">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="14" spans="4:10" x14ac:dyDescent="0.3">
-      <c r="D14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14">
-        <v>0.877</v>
-      </c>
-      <c r="H14">
-        <v>2.33</v>
-      </c>
-      <c r="I14">
-        <v>0.96</v>
-      </c>
-      <c r="J14">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="15" spans="4:10" x14ac:dyDescent="0.3">
-      <c r="D15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15">
-        <v>0.83799999999999997</v>
-      </c>
-      <c r="H15">
-        <v>2</v>
-      </c>
-      <c r="I15">
-        <v>0.92</v>
-      </c>
-      <c r="J15">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="16" spans="4:10" x14ac:dyDescent="0.3">
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16">
-        <v>0.83799999999999997</v>
-      </c>
-      <c r="H16">
-        <v>2</v>
-      </c>
-      <c r="I16">
-        <v>0.92</v>
-      </c>
-      <c r="J16">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="17" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17">
-        <v>0.83799999999999997</v>
-      </c>
-      <c r="H17">
-        <v>2</v>
-      </c>
-      <c r="I17">
-        <v>0.92</v>
-      </c>
-      <c r="J17">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="18" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18">
-        <v>5.1109999999999998</v>
-      </c>
-      <c r="H18">
-        <v>4.93</v>
-      </c>
-      <c r="I18">
-        <v>1.66</v>
-      </c>
-      <c r="J18">
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="K18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D19" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" t="s">
-        <v>24</v>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19">
+        <v>1.88</v>
+      </c>
+      <c r="E19">
+        <v>3.38</v>
+      </c>
+      <c r="F19">
+        <v>1.17</v>
       </c>
       <c r="G19">
-        <v>4.7069999999999999</v>
-      </c>
-      <c r="H19">
-        <v>4.93</v>
-      </c>
-      <c r="I19">
-        <v>1.66</v>
-      </c>
-      <c r="J19">
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="K19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" t="s">
-        <v>22</v>
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20">
+        <v>1.196</v>
+      </c>
+      <c r="E20">
+        <v>2.8</v>
+      </c>
+      <c r="F20">
+        <v>1.05</v>
       </c>
       <c r="G20">
-        <v>5.1109999999999998</v>
-      </c>
-      <c r="H20">
-        <v>4.93</v>
-      </c>
-      <c r="I20">
-        <v>1.66</v>
-      </c>
-      <c r="J20">
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="K20" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" t="s">
-        <v>27</v>
-      </c>
-      <c r="G21">
-        <v>3.8079999999999998</v>
-      </c>
-      <c r="H21">
-        <v>4.7699999999999996</v>
-      </c>
-      <c r="I21">
-        <v>1.63</v>
-      </c>
-      <c r="J21">
-        <v>2.36</v>
-      </c>
-      <c r="K21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D22" t="s">
-        <v>28</v>
-      </c>
-      <c r="E22" t="s">
-        <v>29</v>
-      </c>
-      <c r="G22">
-        <v>1.196</v>
-      </c>
-      <c r="H22">
-        <v>2.8</v>
-      </c>
-      <c r="I22">
-        <v>1.05</v>
-      </c>
-      <c r="J22">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="23" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" t="s">
-        <v>31</v>
-      </c>
-      <c r="G23">
-        <v>1.88</v>
-      </c>
-      <c r="H23">
-        <v>3.38</v>
-      </c>
-      <c r="I23">
-        <v>1.17</v>
-      </c>
-      <c r="J23">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="24" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D24" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" t="s">
-        <v>31</v>
-      </c>
-      <c r="G24">
-        <v>1.88</v>
-      </c>
-      <c r="H24">
-        <v>3.38</v>
-      </c>
-      <c r="I24">
-        <v>1.17</v>
-      </c>
-      <c r="J24">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="25" spans="4:11" x14ac:dyDescent="0.3">
-      <c r="D25" t="s">
-        <v>33</v>
-      </c>
-      <c r="E25" t="s">
-        <v>29</v>
-      </c>
-      <c r="G25">
-        <v>1.196</v>
-      </c>
-      <c r="H25">
-        <v>2.8</v>
-      </c>
-      <c r="I25">
-        <v>1.05</v>
-      </c>
-      <c r="J25">
         <v>1.68</v>
       </c>
     </row>
